--- a/data/trans_bre/IP12-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 6,8</t>
+          <t>-5,03; 6,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 9,04</t>
+          <t>-2,94; 9,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 8,72</t>
+          <t>-2,46; 8,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 5,99</t>
+          <t>-8,91; 6,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 138,54</t>
+          <t>-51,87; 118,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 142,94</t>
+          <t>-26,82; 139,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 241,79</t>
+          <t>-34,83; 218,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,2; 127,57</t>
+          <t>-65,11; 154,17</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,94</t>
+          <t>-5,13; 2,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,48</t>
+          <t>-5,01; 3,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 8,47</t>
+          <t>-0,3; 8,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 4,45</t>
+          <t>-4,96; 4,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,02; 31,42</t>
+          <t>-52,71; 34,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 48,99</t>
+          <t>-44,64; 44,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 155,06</t>
+          <t>-5,99; 155,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,35; 70,65</t>
+          <t>-46,08; 64,39</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 7,06</t>
+          <t>-3,97; 6,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 6,91</t>
+          <t>-2,86; 6,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 3,23</t>
+          <t>-5,41; 3,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 6,3</t>
+          <t>-2,99; 6,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 159,98</t>
+          <t>-46,3; 138,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 158,44</t>
+          <t>-35,24; 174,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,2; 66,25</t>
+          <t>-56,95; 64,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 127,5</t>
+          <t>-33,42; 130,26</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,34</t>
+          <t>-2,32; 3,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 1,46</t>
+          <t>-7,6; 1,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,2</t>
+          <t>-3,72; 4,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,76</t>
+          <t>-6,12; 1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,04; 127,03</t>
+          <t>-48,05; 163,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,16; 29,12</t>
+          <t>-69,11; 20,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,55; 170,97</t>
+          <t>-55,5; 142,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,63; 31,98</t>
+          <t>-63,22; 33,09</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,92</t>
+          <t>-2,15; 2,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,66</t>
+          <t>-2,3; 2,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,59</t>
+          <t>-0,92; 3,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,02</t>
+          <t>-3,41; 1,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 34,59</t>
+          <t>-29,14; 37,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 38,39</t>
+          <t>-24,42; 35,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 66,05</t>
+          <t>-13,28; 69,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,8; 31,32</t>
+          <t>-37,01; 24,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 6,02</t>
+          <t>-4,99; 6,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 9,19</t>
+          <t>-2,86; 9,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 8,19</t>
+          <t>-2,7; 7,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 6,8</t>
+          <t>-9,6; 6,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,87; 118,96</t>
+          <t>-48,32; 135,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 139,8</t>
+          <t>-26,97; 147,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 218,9</t>
+          <t>-32,99; 200,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-65,11; 154,17</t>
+          <t>-69,63; 144,91</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 2,03</t>
+          <t>-5,54; 1,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,41</t>
+          <t>-5,22; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 8,2</t>
+          <t>-0,41; 7,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 4,15</t>
+          <t>-5,01; 4,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,71; 34,55</t>
+          <t>-54,19; 35,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,64; 44,5</t>
+          <t>-43,26; 55,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 155,04</t>
+          <t>-6,22; 136,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,08; 64,39</t>
+          <t>-45,54; 70,76</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 6,52</t>
+          <t>-3,78; 7,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 6,99</t>
+          <t>-2,52; 7,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 3,39</t>
+          <t>-5,51; 3,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 6,3</t>
+          <t>-3,09; 6,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,3; 138,4</t>
+          <t>-41,22; 163,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 174,71</t>
+          <t>-31,51; 174,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-56,95; 64,34</t>
+          <t>-57,74; 81,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 130,26</t>
+          <t>-35,8; 132,7</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,68</t>
+          <t>-2,56; 3,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,1</t>
+          <t>-7,48; 1,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 4,06</t>
+          <t>-3,56; 4,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 1,81</t>
+          <t>-6,85; 1,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,05; 163,26</t>
+          <t>-52,62; 149,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,11; 20,08</t>
+          <t>-68,68; 21,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 142,75</t>
+          <t>-56,29; 158,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,22; 33,09</t>
+          <t>-64,43; 28,0</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,2</t>
+          <t>-2,13; 2,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,58</t>
+          <t>-2,32; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,61</t>
+          <t>-0,75; 3,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,66</t>
+          <t>-3,1; 1,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 37,08</t>
+          <t>-28,68; 39,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 35,66</t>
+          <t>-24,44; 34,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 69,14</t>
+          <t>-9,82; 68,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 24,54</t>
+          <t>-35,27; 23,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-11,84%</t>
+          <t>-10,29%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 6,56</t>
+          <t>-4,29; 6,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 9,16</t>
+          <t>-2,74; 9,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,69</t>
+          <t>-1,84; 8,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 6,62</t>
+          <t>-8,77; 6,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,32; 135,04</t>
+          <t>-45,75; 138,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 147,52</t>
+          <t>-23,11; 142,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,99; 200,0</t>
+          <t>-25,5; 241,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,63; 144,91</t>
+          <t>-67,7; 133,03</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-5,21%</t>
+          <t>-3,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 1,95</t>
+          <t>-5,03; 1,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 4,02</t>
+          <t>-5,13; 3,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,89</t>
+          <t>-0,17; 8,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 4,5</t>
+          <t>-5,38; 5,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,19; 35,46</t>
+          <t>-52,02; 31,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 55,38</t>
+          <t>-44,6; 48,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 136,55</t>
+          <t>-3,61; 155,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 70,76</t>
+          <t>-47,9; 77,28</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 7,3</t>
+          <t>-3,67; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 7,52</t>
+          <t>-3,01; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 3,6</t>
+          <t>-5,61; 3,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,47</t>
+          <t>-3,71; 6,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 163,04</t>
+          <t>-41,63; 159,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 174,15</t>
+          <t>-36,67; 158,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-57,74; 81,33</t>
+          <t>-57,2; 66,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 132,7</t>
+          <t>-38,78; 122,42</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,12</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-28,66%</t>
+          <t>-23,38%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,56</t>
+          <t>-2,71; 3,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 1,14</t>
+          <t>-7,55; 1,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 4,04</t>
+          <t>-3,62; 4,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 1,42</t>
+          <t>-5,49; 2,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 149,14</t>
+          <t>-52,04; 127,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 21,3</t>
+          <t>-69,16; 29,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,29; 158,85</t>
+          <t>-53,55; 170,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 28,0</t>
+          <t>-56,64; 42,31</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-8,4%</t>
+          <t>-6,16%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,07</t>
+          <t>-2,21; 1,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,55</t>
+          <t>-2,15; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,63</t>
+          <t>-0,75; 3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,47</t>
+          <t>-3,06; 2,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 39,18</t>
+          <t>-29,64; 34,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 34,03</t>
+          <t>-22,12; 38,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 68,11</t>
+          <t>-10,04; 66,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 23,05</t>
+          <t>-33,67; 32,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP12-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP12-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,18</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-10,29%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.920388290329309</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.175732109981019</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.056712025244891</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.9138864436616462</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1198298336835361</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.3503262108041783</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.5132128883027048</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1028810874410598</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,29; 6,8</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,74; 9,04</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-1,84; 8,72</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,77; 6,37</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-45,75; 138,54</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-23,11; 142,94</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-25,5; 241,79</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-67,7; 133,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.289352344807734</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.736749767697087</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.839117518783751</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.766245988302289</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.457536348001911</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2310989920453616</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2550453639841368</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6769855443691478</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.803637676845586</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.037137144369915</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.716453688402344</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.373761352278154</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.385364323876827</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.42941453770029</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.417898579234908</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.330317484509443</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,77</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-20,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-8,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>51,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-3,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,03; 1,94</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,13; 3,48</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,17; 8,47</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,38; 5,02</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-52,02; 31,42</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-44,6; 48,99</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-3,61; 155,06</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-47,9; 77,28</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.661108309195744</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.7699484102217713</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.765752969256811</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3367821744669125</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2075646372239577</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.08245504665591329</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.5149259793657209</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.03817426996746983</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,48</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>38,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-14,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,69%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.029820329663679</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.129002793315072</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.1692089325143361</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.380914016645454</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5202026585744324</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4460102620226384</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.03608334154904114</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4790351075418758</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 7,06</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 6,91</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,61; 3,23</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,71; 6,07</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-41,63; 159,98</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-36,67; 158,44</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-57,2; 66,25</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-38,78; 122,42</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.939676758273151</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.484429181663184</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.470971625567882</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.022592370501391</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3142352705130003</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.48991763489588</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.550621983162683</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.7728045469190838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,03</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-36,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-23,38%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.378919240664082</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.475377110482639</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.079918186325034</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.354919517197352</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1957595753579471</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3839943733002049</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.1450058231972274</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1868816047547644</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,71; 3,34</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,55; 1,46</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 4,2</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,49; 2,2</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-52,04; 127,03</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-69,16; 29,12</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-53,55; 170,97</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-56,64; 42,31</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.666402375741422</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.008854930222022</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.614618675778993</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.705792641263478</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.416347276009387</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3667060715214237</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.5720297057651581</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3878016723686619</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.064703944301796</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.913376392598708</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.230044480349031</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.072935890121587</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.599842199023159</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.584413051956172</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.662519259242968</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.224152041016967</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3108787358562841</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.0316626828383</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2331185845742677</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.79823096775228</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.08219227719324509</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3640374192876232</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.04965881472993935</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2337970833505623</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.706601006440485</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-7.55254726147932</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.624864504382071</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.490813087524348</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5203944864250041</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6915916442521745</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.535469680799318</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5664368477302539</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.338857542952357</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.461930714220613</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.20295624383346</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.201555322685862</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.270333324228077</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2911777218544587</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.709692652027981</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.4230870218732606</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,75%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-6,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,21; 1,92</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 2,66</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,75; 3,59</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-3,06; 2,06</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-29,64; 34,59</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-22,12; 38,39</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-10,04; 66,05</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-33,67; 32,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.1147717697033451</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1804613539378427</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.40937149207503</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.487199138722888</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.01750188384014395</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.02139362066414612</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.2165263762158409</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.06162787995729137</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.206801419605962</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.151125009023063</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.7479569944202287</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-3.061571389417888</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2964060674268426</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2212374071580492</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1003701485290753</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3366875108256424</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.917584850197737</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.662645364972534</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.592376150912641</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.056827975774822</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.345938939269315</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3838738921770491</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.6605083465516295</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3226190118822938</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
